--- a/artfynd/A 33655-2023 artfynd.xlsx
+++ b/artfynd/A 33655-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33655-2023 artfynd.xlsx
+++ b/artfynd/A 33655-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>112035020</v>
       </c>
       <c r="B2" t="n">
-        <v>89550</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -712,7 +707,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lövnäs (Lövnäs), Ås lm</t>
+          <t>Lövnäs, Lövnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -803,15 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112038473</v>
+        <v>112037635</v>
       </c>
       <c r="B3" t="n">
-        <v>89835</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,44 +809,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövnäs (Lövnäs), Ås lm</t>
+          <t>Lövnäs, Lövnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516057</v>
+        <v>515886</v>
       </c>
       <c r="R3" t="n">
-        <v>7184320</v>
+        <v>7184226</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -898,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -950,15 +931,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112037684</v>
+        <v>112038134</v>
       </c>
       <c r="B4" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,35 +942,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lövnäs (Lövnäs), Ås lm</t>
+          <t>Lövnäs, Lövnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515886</v>
+        <v>515925</v>
       </c>
       <c r="R4" t="n">
-        <v>7184226</v>
+        <v>7184319</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1036,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1026,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Blåbärsgranskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1065,12 +1041,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1088,51 +1064,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112037208</v>
+        <v>112038082</v>
       </c>
       <c r="B5" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lövnäs (Lövnäs), Ås lm</t>
+          <t>Lövnäs, Lövnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516097</v>
+        <v>515925</v>
       </c>
       <c r="R5" t="n">
-        <v>7184259</v>
+        <v>7184319</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1164,7 +1135,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1174,7 +1145,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1188,7 +1159,17 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1198,7 +1179,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1216,15 +1197,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112035549</v>
+        <v>112037884</v>
       </c>
       <c r="B6" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,35 +1208,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövnäs (Lövnäs), Ås lm</t>
+          <t>Lövnäs, Lövnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515977</v>
+        <v>515873</v>
       </c>
       <c r="R6" t="n">
-        <v>7184567</v>
+        <v>7184350</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1292,7 +1270,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1302,7 +1280,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1311,22 +1289,13 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1344,51 +1313,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112038436</v>
+        <v>112037684</v>
       </c>
       <c r="B7" t="n">
-        <v>89550</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lövnäs (Lövnäs), Ås lm</t>
+          <t>Lövnäs, Lövnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515951</v>
+        <v>515886</v>
       </c>
       <c r="R7" t="n">
-        <v>7184320</v>
+        <v>7184226</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1420,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1430,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1444,7 +1408,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Blåbärsgranskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1482,51 +1446,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112038134</v>
+        <v>112038529</v>
       </c>
       <c r="B8" t="n">
-        <v>90560</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lövnäs (Lövnäs), Ås lm</t>
+          <t>Lövnäs, Lövnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515925</v>
+        <v>515871</v>
       </c>
       <c r="R8" t="n">
-        <v>7184319</v>
+        <v>7184628</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1558,7 +1517,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1568,7 +1527,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1582,27 +1541,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1620,51 +1559,55 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112038082</v>
+        <v>112038473</v>
       </c>
       <c r="B9" t="n">
-        <v>90236</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lövnäs (Lövnäs), Ås lm</t>
+          <t>Lövnäs, Lövnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515925</v>
+        <v>516058</v>
       </c>
       <c r="R9" t="n">
-        <v>7184319</v>
+        <v>7184320</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1696,7 +1639,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1706,7 +1649,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1735,12 +1678,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1758,15 +1701,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112037386</v>
+        <v>112038436</v>
       </c>
       <c r="B10" t="n">
-        <v>89572</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,35 +1712,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lövnäs (Lövnäs), Ås lm</t>
+          <t>Lövnäs, Lövnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516032</v>
+        <v>515952</v>
       </c>
       <c r="R10" t="n">
-        <v>7184227</v>
+        <v>7184319</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1834,7 +1772,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1844,7 +1782,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1858,7 +1796,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Blåbärsgranskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1873,12 +1811,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1896,15 +1834,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112037635</v>
+        <v>112035981</v>
       </c>
       <c r="B11" t="n">
-        <v>89550</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1912,38 +1845,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lövnäs (Lövnäs), Ås lm</t>
+          <t>Lövnäs, Lövnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515886</v>
+        <v>516149</v>
       </c>
       <c r="R11" t="n">
-        <v>7184226</v>
+        <v>7184413</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1972,7 +1905,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1982,7 +1915,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1996,27 +1929,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2034,19 +1947,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112038529</v>
+        <v>112035549</v>
       </c>
       <c r="B12" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2071,14 +1979,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lövnäs (Lövnäs), Ås lm</t>
+          <t>Lövnäs, Lövnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515872</v>
+        <v>515977</v>
       </c>
       <c r="R12" t="n">
-        <v>7184628</v>
+        <v>7184567</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2110,7 +2018,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2120,7 +2028,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2134,7 +2042,17 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2152,54 +2070,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112035981</v>
+        <v>112037208</v>
       </c>
       <c r="B13" t="n">
-        <v>91626</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lövnäs (Lövnäs), Ås lm</t>
+          <t>Lövnäs, Lövnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516149</v>
+        <v>516097</v>
       </c>
       <c r="R13" t="n">
-        <v>7184413</v>
+        <v>7184258</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2228,7 +2141,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2238,7 +2151,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2253,6 +2166,16 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2267,127 +2190,6 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>112037884</v>
-      </c>
-      <c r="B14" t="n">
-        <v>91626</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>5964</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Sarcodon imbricatus s.str.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Lövnäs (Lövnäs), Ås lm</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>515873</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7184350</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2023-09-11</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2023-09-11</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33655-2023 artfynd.xlsx
+++ b/artfynd/A 33655-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -814,6 +819,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038473</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -937,6 +947,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112035020</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1070,6 +1085,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037635</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1203,6 +1223,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038436</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1336,6 +1361,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038134</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1469,6 +1499,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038082</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1582,6 +1617,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112035981</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1698,6 +1738,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037884</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1821,6 +1866,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112035549</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1944,6 +1994,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037208</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2077,6 +2132,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112037684</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2190,8 +2250,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038529</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>